--- a/src/excel-data/special.xlsx
+++ b/src/excel-data/special.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/Cao Yuxuan/テストweb/findmyrailpass.net/src/excel-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DC9501-C92E-1443-8823-1DBFDD8EDEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACD8E18-F5E9-B046-874E-5DCDD0E14215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10900" yWindow="3040" windowWidth="27500" windowHeight="16360" xr2:uid="{AE1F6D79-7BF8-3141-82A4-F48A6B9BD987}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="95">
   <si>
     <t>sortOrder</t>
   </si>
@@ -613,12 +613,253 @@
   <si>
     <t>ムーミンバレーパークおでかけパス（スマートフォン）</t>
   </si>
+  <si>
+    <t>トキ鉄ツアーパス</t>
+  </si>
+  <si>
+    <r>
+      <t>※坐普通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>以外需另外加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+※「えちごトキめきリゾート雪月花」不可使用</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>regional</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>/images/coverage/Tokitetsu-Tour-Pass.png</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">票; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>票；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>站</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>票；</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>越后铁道旅游周游券</t>
+  </si>
+  <si>
+    <t>Tokitetsu-Tour-Pass</t>
+  </si>
+  <si>
+    <t>Fukutetsu-Premium-65Plus</t>
+  </si>
+  <si>
+    <t>65岁以上高级1日券</t>
+  </si>
+  <si>
+    <t>/images/coverage/Fukutetsu-Premium-65Plus.png</t>
+  </si>
+  <si>
+    <r>
+      <t>普通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://fukutetsu.jp/train/tickets1.php#collapse1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://pass.ryde-go.com/products/9Z78QWVS028N</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>プレミア1日フリー乗車券(65歳以上)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -684,6 +925,12 @@
       <name val="黒体-簡 ミディアム"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -716,7 +963,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -733,6 +980,12 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1068,13 +1321,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD3AD49-5E2D-8B43-89DC-9E00774DC229}">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="3" max="3" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1">
+    <row r="1" spans="1:35" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1160,7 +1413,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:30" s="1" customFormat="1">
+    <row r="2" spans="1:35" s="1" customFormat="1">
       <c r="B2" s="1" t="s">
         <v>33</v>
       </c>
@@ -1228,7 +1481,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="1" customFormat="1">
+    <row r="3" spans="1:35" s="1" customFormat="1">
       <c r="B3" s="1" t="s">
         <v>40</v>
       </c>
@@ -1296,7 +1549,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="1" customFormat="1">
+    <row r="4" spans="1:35" s="1" customFormat="1">
       <c r="B4" s="1" t="s">
         <v>45</v>
       </c>
@@ -1364,7 +1617,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="1" customFormat="1">
+    <row r="5" spans="1:35" s="1" customFormat="1">
       <c r="B5" s="1" t="s">
         <v>51</v>
       </c>
@@ -1432,7 +1685,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:35">
       <c r="B6" s="1" t="s">
         <v>61</v>
       </c>
@@ -1449,7 +1702,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:35">
       <c r="B7" s="1" t="s">
         <v>58</v>
       </c>
@@ -1466,7 +1719,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="4" customFormat="1">
+    <row r="8" spans="1:35" s="4" customFormat="1">
       <c r="B8" s="4" t="s">
         <v>62</v>
       </c>
@@ -1534,7 +1787,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:30" s="7" customFormat="1">
+    <row r="9" spans="1:35" s="7" customFormat="1">
       <c r="A9" s="7">
         <v>57</v>
       </c>
@@ -1582,6 +1835,100 @@
       </c>
       <c r="AD9" s="8" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" s="1" customFormat="1" ht="168">
+      <c r="B10" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="15">
+        <v>2400</v>
+      </c>
+      <c r="G10" s="15">
+        <v>1200</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T10" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI10" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" s="1" customFormat="1">
+      <c r="B11" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="15">
+        <v>500</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="O11" s="1">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T11" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>3</v>
+      </c>
+      <c r="AI11" s="12" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1591,6 +1938,8 @@
     <hyperlink ref="X8" r:id="rId2" xr:uid="{4E5B9664-04A6-1A40-A582-1CD9AC414B7E}"/>
     <hyperlink ref="X9" r:id="rId3" xr:uid="{7AF66FAA-2C7E-B445-A911-A58BE5A93699}"/>
     <hyperlink ref="W9" r:id="rId4" xr:uid="{11206038-1CD7-F547-AAB5-768FA4F6AEA9}"/>
+    <hyperlink ref="W11" r:id="rId5" location="collapse1" xr:uid="{77C93FE4-BEAA-D842-9FFF-A6C04217C53D}"/>
+    <hyperlink ref="X11" r:id="rId6" xr:uid="{DB8762DF-5C1A-B347-B26B-FA66A4FF7AF0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
